--- a/data/clients.xlsx
+++ b/data/clients.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hoffmann-my.sharepoint.com/personal/lucian_ilade_hoffmann-group_com/Documents/Documentos/Proyectos/pedidos_eb/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iladel\Downloads\abril\23\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="11_F25DC773A252ABDACC10484161DD59B05BDE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7853FF4E-9467-4D1C-95F4-61E55BA3FB50}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B6E8D30-0AB6-4EF1-A86A-E95F8122EC0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2655" yWindow="3390" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="14">
   <si>
     <t>Patentes Talgo, S.L.U. Centro: 86 TALLERES MTO. ALTA VELOCIDAD Antonio Cabezón s/n 28034 Madrid-Madrid España</t>
   </si>
@@ -61,6 +61,12 @@
   </si>
   <si>
     <t>ES</t>
+  </si>
+  <si>
+    <t>TE COMPONENTES ELECTROMECÂNICOS LDA Estrada de Almeirim 7009-505 EVORA PORTUGAL</t>
+  </si>
+  <si>
+    <t>PT</t>
   </si>
 </sst>
 </file>
@@ -96,8 +102,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -378,10 +387,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="88.85546875" customWidth="1"/>
+    <col min="1" max="1" width="112.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="46.5703125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -482,6 +491,17 @@
       </c>
       <c r="C9" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10">
+        <v>7102671400</v>
+      </c>
+      <c r="C10" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/data/clients.xlsx
+++ b/data/clients.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iladel\Downloads\abril\23\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hoffmann-my.sharepoint.com/personal/lucian_ilade_hoffmann-group_com/Documents/Documentos/Proyectos/pedidos_eb/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B6E8D30-0AB6-4EF1-A86A-E95F8122EC0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="72" documentId="11_F25DC773A252ABDACC10484161DD59B05BDE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{58FF18D8-C8F4-4A36-A530-096A24E48747}"/>
   <bookViews>
-    <workbookView xWindow="2655" yWindow="3390" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="45972" yWindow="612" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="58">
   <si>
     <t>Patentes Talgo, S.L.U. Centro: 86 TALLERES MTO. ALTA VELOCIDAD Antonio Cabezón s/n 28034 Madrid-Madrid España</t>
   </si>
@@ -63,23 +63,204 @@
     <t>ES</t>
   </si>
   <si>
-    <t>TE COMPONENTES ELECTROMECÂNICOS LDA Estrada de Almeirim 7009-505 EVORA PORTUGAL</t>
+    <t>Becton Dickinson, S.A. Camino de Valdeoliva S/N 28750 San Agustin del Guadalix</t>
+  </si>
+  <si>
+    <t>Brose Sitech, Unipessoal Lda. Nuno Silva / OC-PA/PT . Quinta da Marquesa IV P-2950-677 QUINTA DO ANJO</t>
+  </si>
+  <si>
+    <t>Brose Sitech, Unipessoal Lda. Manuel Bragadeste / OC-PA/PT . Quinta da Marquesa IV P-2950-677 QUINTA DO ANJO</t>
+  </si>
+  <si>
+    <t>Brose Sitech Palmela Paula Vieira / OC-PA/PQ . Quinta da Marquesa IV P-2950-677 QUINTA DO ANJO</t>
+  </si>
+  <si>
+    <t>Brose Sitech, Unipessoal Lda. Orlando Mendes / OC-PA/PP . Quinta da Marquesa IV P-2950-677 QUINTA DO ANJO</t>
+  </si>
+  <si>
+    <t>Empresa Brose Sitech, Unipessoal Lda. Nuno Silva Quinta da Marquesa IV P-2950-677 QUINTA DO ANJO</t>
+  </si>
+  <si>
+    <t>Brose Sitech, Unipessoal Lda. Paula Vieira / OC-PA/PQ . Quinta da Marquesa IV P-2950-677 QUINTA DO ANJO</t>
+  </si>
+  <si>
+    <t>Rua Max Brose NÂº 38 ZIM do Lajedo P-3465-158 SANTIAGO DE BESTEIROS/TONDELA</t>
+  </si>
+  <si>
+    <t>Brose Sitech Palmela Manuel Bragadeste / OC-PA/PT . Quinta da Marquesa IV P-2950-677 QUINTA DO ANJO</t>
   </si>
   <si>
     <t>PT</t>
+  </si>
+  <si>
+    <t>Local: Serpins 3200-355 SERPINS</t>
+  </si>
+  <si>
+    <t>Local: Zona Industrial Alto do PadrÃ£o 3200-133 LOUSÃƒ</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Site 2586</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Site 2501</t>
+  </si>
+  <si>
+    <t>Patentes Talgo, S.L.U. Centro: 86 TALLERES MTO. ALTA VELOCIDAD Antonio CabezÃ³n s/n 28034 Madrid-Madrid EspaÃ±a</t>
+  </si>
+  <si>
+    <t>62 Las Matas 2 (Ctra. La CoruÃ±a Km. 23 Paseo del tren Talgo nÂº 2 28290 Las Rozas-Madrid EspaÃ±a</t>
+  </si>
+  <si>
+    <t>En nuestro centro de MÃLAGA-TALLERES MANTENIMIENTO AVE Camino de los Prados - C/ Ucrania . 29006 , MÃ¡laga - MÃ¡laga</t>
+  </si>
+  <si>
+    <t>Patentes Talgo, S.L.U. Centro: 05 Rivabellosa Rio Bayas 5 01213 Rivabellosa-Ãlava EspaÃ±a</t>
+  </si>
+  <si>
+    <t>Patentes Talgo, S.L.U. Centro: 62 Las Matas 2 (Ctra. La CoruÃ±a Km. 23 Paseo del tren Talgo nÂº 2 28290 Las Rozas-Madrid EspaÃ±a</t>
+  </si>
+  <si>
+    <t>Ctra. Yepes, Km8, 4 . 45300 , OcaÃ±a - Toledo</t>
+  </si>
+  <si>
+    <t>Pol. Ind. Dehesa de la Plata . AutovÃ­a A4, Km 52 45340 , OntÃ­gola - Toledo</t>
+  </si>
+  <si>
+    <t>Carretera de La CoruÃ±a KM. 22 . 28230 , Las Rozas - Madrid</t>
+  </si>
+  <si>
+    <t>InstalaÃ§Ãµes da MDA</t>
+  </si>
+  <si>
+    <t>InstalaÃ§Ãµes da Ulmolde</t>
+  </si>
+  <si>
+    <t>InstalaÃ§Ãµes da Simoldes AÃ§os</t>
+  </si>
+  <si>
+    <t>InstalaÃ§Ãµes da Mecamolde</t>
+  </si>
+  <si>
+    <t>InstalaÃ§Ãµes da IGM</t>
+  </si>
+  <si>
+    <t>InstalaÃ§Ãµes da IMA</t>
+  </si>
+  <si>
+    <t>InstalaÃ§Ãµes da Simoldes Steel Center</t>
+  </si>
+  <si>
+    <t>Accelleron Iberia S.L.U. Calle Bergantin 22-24 nave 8 11379 P.I Palmones</t>
+  </si>
+  <si>
+    <t>Accelleron Iberia S.L. Los Llanos de Jerez 8 28823 Coslada</t>
+  </si>
+  <si>
+    <t>Accelleron Iberia S.L. Calle Bergantin 22-24 nave 8 11379 P.I Palmones</t>
+  </si>
+  <si>
+    <t>Turbo Systems Iberia, S.L.U. Calle de Ibarra &amp; Cia DÃ¡rsena exterior s/n 35008 Las Palmas-Puerto de la Luz</t>
+  </si>
+  <si>
+    <t>Turbo Systems Iberia, S.L.U. Los Llanos de Jerez 8 28823 Coslada</t>
+  </si>
+  <si>
+    <t>MAHON Cos Nou s/n 07703 MAHÃ“N (Illes Balears) 07</t>
+  </si>
+  <si>
+    <t>BARRANCO CT de Barranco Tirajana 35107 S. BARTOLOME DE TIRAJANA 35</t>
+  </si>
+  <si>
+    <t>GRANADILLA P.INDUSTRIAL GRANADILLA, KM-50 38594 CHIMICHE-GRANADILLA (Tene 38</t>
+  </si>
+  <si>
+    <t>DOW PORTUGAL PROD QUIMICO EST PMDI ISOCIANATO POLIMER PM EST PMDI ISOCIANATO c/o DOW PORTUGAL PRODUTOS QUIMICOS RUA DO RIO ANTUA, Nr. 1 3860-529 ESTARREJA PORTUGAL</t>
+  </si>
+  <si>
+    <r>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Open Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t>Automotive Interior Syst. Estrada Nacional 4 P-7050-001 MONTEMOR-O-NOVO</t>
+    </r>
+  </si>
+  <si>
+    <t>Avda. Madrid, 54. 28802 ALCALÁ DE HENARES (Madrid) Spain.</t>
+  </si>
+  <si>
+    <t>TORRE GAS, S.L. Av. Maresme, 122 08918 BADALONA Barcelona España</t>
+  </si>
+  <si>
+    <r>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Open Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t>Av. Maresme, 122 08918 BARCELONA (España)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Open Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t>7105834</t>
+    </r>
+  </si>
+  <si>
+    <t>Talleres Eléctricos M. Serrano S.A.U. Poligono Industrial de Ambrosero, Parcela 3,1 39791 Ambrosero-Bárcena de Cicero (Cantabria)</t>
+  </si>
+  <si>
+    <t>Area Industrial de Llobregat C\Argent 1 , 08755 Castelbisbal</t>
+  </si>
+  <si>
+    <t>ES-GAVA-100-S Calle Barcelona, 3 Gavà Barcelona 08850</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Open Sans"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Open Sans"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -102,11 +283,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -122,6 +302,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -387,7 +571,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C54"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="112.5703125" bestFit="1" customWidth="1"/>
@@ -494,18 +678,497 @@
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
         <v>12</v>
       </c>
       <c r="B10">
-        <v>7102671400</v>
+        <v>7104108</v>
       </c>
       <c r="C10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>13</v>
+      </c>
+      <c r="B11">
+        <v>7123092</v>
+      </c>
+      <c r="C11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12">
+        <v>7123092</v>
+      </c>
+      <c r="C12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13">
+        <v>7123092</v>
+      </c>
+      <c r="C13" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14">
+        <v>7123092</v>
+      </c>
+      <c r="C14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15">
+        <v>7123092</v>
+      </c>
+      <c r="C15" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16">
+        <v>7123092</v>
+      </c>
+      <c r="C16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17">
+        <v>7102724</v>
+      </c>
+      <c r="C17" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18">
+        <v>7123092</v>
+      </c>
+      <c r="C18" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19">
+        <v>7101205</v>
+      </c>
+      <c r="C19" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20">
+        <v>7101205100</v>
+      </c>
+      <c r="C20" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>24</v>
+      </c>
+      <c r="B21">
+        <v>7115154</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22">
+        <v>7103009</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23">
+        <v>7107399200</v>
+      </c>
+      <c r="C23" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>27</v>
+      </c>
+      <c r="B24">
+        <v>7107399</v>
+      </c>
+      <c r="C24" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>28</v>
+      </c>
+      <c r="B25">
+        <v>7107575</v>
+      </c>
+      <c r="C25" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>29</v>
+      </c>
+      <c r="B26">
+        <v>7107405</v>
+      </c>
+      <c r="C26" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>30</v>
+      </c>
+      <c r="B27">
+        <v>7107399</v>
+      </c>
+      <c r="C27" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>31</v>
+      </c>
+      <c r="B28">
+        <v>7107399500</v>
+      </c>
+      <c r="C28" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>32</v>
+      </c>
+      <c r="B29">
+        <v>7107399400</v>
+      </c>
+      <c r="C29" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>33</v>
+      </c>
+      <c r="B30">
+        <v>7107399100</v>
+      </c>
+      <c r="C30" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>34</v>
+      </c>
+      <c r="B31">
+        <v>7114446</v>
+      </c>
+      <c r="C31" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>35</v>
+      </c>
+      <c r="B32">
+        <v>7115297</v>
+      </c>
+      <c r="C32" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>36</v>
+      </c>
+      <c r="B33">
+        <v>7114654</v>
+      </c>
+      <c r="C33" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34">
+        <v>7115298</v>
+      </c>
+      <c r="C34" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35">
+        <v>7114697</v>
+      </c>
+      <c r="C35" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>39</v>
+      </c>
+      <c r="B36">
+        <v>7115089</v>
+      </c>
+      <c r="C36" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>40</v>
+      </c>
+      <c r="B37">
+        <v>7121379</v>
+      </c>
+      <c r="C37" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38">
+        <v>7120061100</v>
+      </c>
+      <c r="C38" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B39">
+        <v>7119999</v>
+      </c>
+      <c r="C39" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>43</v>
+      </c>
+      <c r="B40">
+        <v>7120061100</v>
+      </c>
+      <c r="C40" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>44</v>
+      </c>
+      <c r="B41">
+        <v>7120060100</v>
+      </c>
+      <c r="C41" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>44</v>
+      </c>
+      <c r="B42">
+        <v>7120060100</v>
+      </c>
+      <c r="C42" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>45</v>
+      </c>
+      <c r="B43">
+        <v>7119999</v>
+      </c>
+      <c r="C43" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>46</v>
+      </c>
+      <c r="B44">
+        <v>7103554106</v>
+      </c>
+      <c r="C44" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>47</v>
+      </c>
+      <c r="B45">
+        <v>7103555109</v>
+      </c>
+      <c r="C45" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>48</v>
+      </c>
+      <c r="B46">
+        <v>7103555104</v>
+      </c>
+      <c r="C46" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A47" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B47">
+        <v>7115248</v>
+      </c>
+      <c r="C47" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A48" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B48">
+        <v>7103617</v>
+      </c>
+      <c r="C48" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A49" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B49">
+        <v>7101157</v>
+      </c>
+      <c r="C49" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A50" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B50" s="1">
+        <v>7105917</v>
+      </c>
+      <c r="C50" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A51" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C51" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A52" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B52">
+        <v>7104999</v>
+      </c>
+      <c r="C52" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A53" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B53">
+        <v>7105429</v>
+      </c>
+      <c r="C53" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A54" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B54">
+        <v>7105429</v>
+      </c>
+      <c r="C54" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter>
     <oddFooter>&amp;R_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K000000 Confidential</oddFooter>
   </headerFooter>

--- a/data/clients.xlsx
+++ b/data/clients.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hoffmann-my.sharepoint.com/personal/lucian_ilade_hoffmann-group_com/Documents/Documentos/Proyectos/pedidos_eb/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="72" documentId="11_F25DC773A252ABDACC10484161DD59B05BDE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{58FF18D8-C8F4-4A36-A530-096A24E48747}"/>
+  <xr:revisionPtr revIDLastSave="80" documentId="11_F25DC773A252ABDACC10484161DD59B05BDE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C580BB3D-86A2-4CE3-A055-3B0AE708041C}"/>
   <bookViews>
-    <workbookView xWindow="45972" yWindow="612" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="59">
   <si>
     <t>Patentes Talgo, S.L.U. Centro: 86 TALLERES MTO. ALTA VELOCIDAD Antonio Cabezón s/n 28034 Madrid-Madrid España</t>
   </si>
@@ -235,6 +235,9 @@
   </si>
   <si>
     <t>ES-GAVA-100-S Calle Barcelona, 3 Gavà Barcelona 08850</t>
+  </si>
+  <si>
+    <t>Serpins  3200-355 SERPINS</t>
   </si>
 </sst>
 </file>
@@ -571,14 +574,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C54"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="112.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="46.5703125" customWidth="1"/>
+    <col min="1" max="1" width="112.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -589,7 +592,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -600,7 +603,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -611,7 +614,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -622,7 +625,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -633,7 +636,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -644,7 +647,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -655,7 +658,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -666,7 +669,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -677,7 +680,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -688,7 +691,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -699,7 +702,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -710,7 +713,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -721,7 +724,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -732,7 +735,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -743,7 +746,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -754,7 +757,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>19</v>
       </c>
@@ -765,7 +768,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -776,7 +779,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>22</v>
       </c>
@@ -787,7 +790,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>23</v>
       </c>
@@ -798,7 +801,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>24</v>
       </c>
@@ -806,7 +809,7 @@
         <v>7115154</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>25</v>
       </c>
@@ -814,7 +817,7 @@
         <v>7103009</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>26</v>
       </c>
@@ -825,7 +828,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>27</v>
       </c>
@@ -836,7 +839,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>28</v>
       </c>
@@ -847,7 +850,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>29</v>
       </c>
@@ -858,7 +861,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>30</v>
       </c>
@@ -869,7 +872,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>31</v>
       </c>
@@ -880,7 +883,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>32</v>
       </c>
@@ -891,7 +894,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>33</v>
       </c>
@@ -902,7 +905,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>34</v>
       </c>
@@ -913,7 +916,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>35</v>
       </c>
@@ -924,7 +927,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>36</v>
       </c>
@@ -935,7 +938,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>37</v>
       </c>
@@ -946,7 +949,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>38</v>
       </c>
@@ -957,7 +960,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>39</v>
       </c>
@@ -968,7 +971,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>40</v>
       </c>
@@ -979,7 +982,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>41</v>
       </c>
@@ -990,7 +993,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>42</v>
       </c>
@@ -1001,7 +1004,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>43</v>
       </c>
@@ -1012,7 +1015,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>44</v>
       </c>
@@ -1023,7 +1026,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>44</v>
       </c>
@@ -1034,7 +1037,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>45</v>
       </c>
@@ -1045,7 +1048,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>46</v>
       </c>
@@ -1056,7 +1059,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>47</v>
       </c>
@@ -1067,7 +1070,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>48</v>
       </c>
@@ -1078,7 +1081,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
         <v>49</v>
       </c>
@@ -1089,7 +1092,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
         <v>50</v>
       </c>
@@ -1100,7 +1103,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
         <v>51</v>
       </c>
@@ -1111,7 +1114,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
         <v>52</v>
       </c>
@@ -1122,7 +1125,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
         <v>53</v>
       </c>
@@ -1133,7 +1136,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
         <v>55</v>
       </c>
@@ -1144,7 +1147,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
         <v>56</v>
       </c>
@@ -1155,7 +1158,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
         <v>57</v>
       </c>
@@ -1164,6 +1167,17 @@
       </c>
       <c r="C54" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>58</v>
+      </c>
+      <c r="B55">
+        <v>7101205</v>
+      </c>
+      <c r="C55" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/data/clients.xlsx
+++ b/data/clients.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hoffmann-my.sharepoint.com/personal/lucian_ilade_hoffmann-group_com/Documents/Documentos/Proyectos/pedidos_eb/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="80" documentId="11_F25DC773A252ABDACC10484161DD59B05BDE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C580BB3D-86A2-4CE3-A055-3B0AE708041C}"/>
+  <xr:revisionPtr revIDLastSave="162" documentId="11_F25DC773A252ABDACC10484161DD59B05BDE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5F07651F-3495-4874-B0F5-F79E17AB95BD}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-135" yWindow="-135" windowWidth="29070" windowHeight="17550" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="78">
   <si>
     <t>Patentes Talgo, S.L.U. Centro: 86 TALLERES MTO. ALTA VELOCIDAD Antonio Cabezón s/n 28034 Madrid-Madrid España</t>
   </si>
@@ -239,12 +239,69 @@
   <si>
     <t>Serpins  3200-355 SERPINS</t>
   </si>
+  <si>
+    <t>Codigo Postal</t>
+  </si>
+  <si>
+    <t>2950-677</t>
+  </si>
+  <si>
+    <t>3200-355</t>
+  </si>
+  <si>
+    <t>01213</t>
+  </si>
+  <si>
+    <t>08918</t>
+  </si>
+  <si>
+    <t>39791</t>
+  </si>
+  <si>
+    <t>08755</t>
+  </si>
+  <si>
+    <t>08850</t>
+  </si>
+  <si>
+    <t>Codigos Proprios</t>
+  </si>
+  <si>
+    <t>VAT/NIF/CIF</t>
+  </si>
+  <si>
+    <t>7005-838</t>
+  </si>
+  <si>
+    <t>7005-841</t>
+  </si>
+  <si>
+    <t>7009-505</t>
+  </si>
+  <si>
+    <t>7005-328</t>
+  </si>
+  <si>
+    <t>7005-513</t>
+  </si>
+  <si>
+    <t>7002-505</t>
+  </si>
+  <si>
+    <t>TE COMPONENTES ELECTROMECÂNICOS LDA Estrada de Almeirim 7009-505 Evora</t>
+  </si>
+  <si>
+    <t>TE Componentes Electromec.LDA Antiga E.N.18 615 7005-838 EVORA PORTUGAL</t>
+  </si>
+  <si>
+    <t>PT501486429</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -261,6 +318,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Open Sans"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
       <color rgb="FF000000"/>
       <name val="Open Sans"/>
       <family val="2"/>
@@ -286,10 +350,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -574,609 +643,829 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:F60"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="112.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="46.5546875" customWidth="1"/>
+    <col min="1" max="1" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="112.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="46.5546875" customWidth="1"/>
+    <col min="6" max="6" width="15.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1" t="s">
         <v>8</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>9</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="F1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B2" s="3">
+        <v>28034</v>
+      </c>
+      <c r="C2" t="s">
         <v>0</v>
       </c>
-      <c r="B2">
+      <c r="D2">
         <v>7107399200</v>
       </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B3" s="3">
+        <v>28290</v>
+      </c>
+      <c r="C3" t="s">
         <v>1</v>
       </c>
-      <c r="B3">
+      <c r="D3">
         <v>7107399</v>
       </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B4" s="3">
+        <v>29006</v>
+      </c>
+      <c r="C4" t="s">
         <v>2</v>
       </c>
-      <c r="B4">
+      <c r="D4">
         <v>7107575</v>
       </c>
-      <c r="C4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="E4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B5" s="3">
+        <v>1213</v>
+      </c>
+      <c r="C5" t="s">
         <v>3</v>
       </c>
-      <c r="B5">
+      <c r="D5">
         <v>7107405</v>
       </c>
-      <c r="C5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="E5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B6" s="3">
+        <v>28290</v>
+      </c>
+      <c r="C6" t="s">
         <v>4</v>
       </c>
-      <c r="B6">
+      <c r="D6">
         <v>7107399</v>
       </c>
-      <c r="C6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="E6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B7" s="3">
+        <v>45300</v>
+      </c>
+      <c r="C7" t="s">
         <v>5</v>
       </c>
-      <c r="B7">
+      <c r="D7">
         <v>7107399500</v>
       </c>
-      <c r="C7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="E7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B8" s="3">
+        <v>45340</v>
+      </c>
+      <c r="C8" t="s">
         <v>6</v>
       </c>
-      <c r="B8">
+      <c r="D8">
         <v>7107399400</v>
       </c>
-      <c r="C8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="E8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B9" s="3">
+        <v>28230</v>
+      </c>
+      <c r="C9" t="s">
         <v>7</v>
       </c>
-      <c r="B9">
+      <c r="D9">
         <v>7107399100</v>
       </c>
-      <c r="C9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="E9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B10" s="3">
+        <v>28750</v>
+      </c>
+      <c r="C10" t="s">
         <v>12</v>
       </c>
-      <c r="B10">
+      <c r="D10">
         <v>7104108</v>
       </c>
-      <c r="C10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="E10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B11" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" t="s">
         <v>13</v>
       </c>
-      <c r="B11">
+      <c r="D11">
         <v>7123092</v>
       </c>
-      <c r="C11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="E11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B12" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12" t="s">
         <v>14</v>
       </c>
-      <c r="B12">
+      <c r="D12">
         <v>7123092</v>
       </c>
-      <c r="C12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="E12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B13" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C13" t="s">
         <v>15</v>
       </c>
-      <c r="B13">
+      <c r="D13">
         <v>7123092</v>
       </c>
-      <c r="C13" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="E13" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B14" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C14" t="s">
         <v>16</v>
       </c>
-      <c r="B14">
+      <c r="D14">
         <v>7123092</v>
       </c>
-      <c r="C14" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+      <c r="E14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B15" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15" t="s">
         <v>17</v>
       </c>
-      <c r="B15">
+      <c r="D15">
         <v>7123092</v>
       </c>
-      <c r="C15" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="E15" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B16" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C16" t="s">
         <v>18</v>
       </c>
-      <c r="B16">
+      <c r="D16">
         <v>7123092</v>
       </c>
-      <c r="C16" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+      <c r="E16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B17" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C17" t="s">
         <v>19</v>
       </c>
-      <c r="B17">
+      <c r="D17">
         <v>7102724</v>
       </c>
-      <c r="C17" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+      <c r="E17" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B18" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C18" t="s">
         <v>20</v>
       </c>
-      <c r="B18">
+      <c r="D18">
         <v>7123092</v>
       </c>
-      <c r="C18" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+      <c r="E18" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B19" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C19" t="s">
         <v>22</v>
       </c>
-      <c r="B19">
+      <c r="D19">
         <v>7101205</v>
       </c>
-      <c r="C19" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+      <c r="E19" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B20" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C20" t="s">
         <v>23</v>
       </c>
-      <c r="B20">
+      <c r="D20">
         <v>7101205100</v>
       </c>
-      <c r="C20" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+      <c r="E20" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B21" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C21" t="s">
         <v>24</v>
       </c>
-      <c r="B21">
+      <c r="D21">
         <v>7115154</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B22" s="3"/>
+      <c r="C22" t="s">
         <v>25</v>
       </c>
-      <c r="B22">
+      <c r="D22">
         <v>7103009</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B23" s="3">
+        <v>28034</v>
+      </c>
+      <c r="C23" t="s">
         <v>26</v>
       </c>
-      <c r="B23">
+      <c r="D23">
         <v>7107399200</v>
       </c>
-      <c r="C23" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+      <c r="E23" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B24" s="3">
+        <v>28290</v>
+      </c>
+      <c r="C24" t="s">
         <v>27</v>
       </c>
-      <c r="B24">
+      <c r="D24">
         <v>7107399</v>
       </c>
-      <c r="C24" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+      <c r="E24" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B25" s="3">
+        <v>29006</v>
+      </c>
+      <c r="C25" t="s">
         <v>28</v>
       </c>
-      <c r="B25">
+      <c r="D25">
         <v>7107575</v>
       </c>
-      <c r="C25" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+      <c r="E25" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B26" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C26" t="s">
         <v>29</v>
       </c>
-      <c r="B26">
+      <c r="D26">
         <v>7107405</v>
       </c>
-      <c r="C26" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+      <c r="E26" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B27" s="3">
+        <v>28290</v>
+      </c>
+      <c r="C27" t="s">
         <v>30</v>
       </c>
-      <c r="B27">
+      <c r="D27">
         <v>7107399</v>
       </c>
-      <c r="C27" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+      <c r="E27" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B28" s="3">
+        <v>45300</v>
+      </c>
+      <c r="C28" t="s">
         <v>31</v>
       </c>
-      <c r="B28">
+      <c r="D28">
         <v>7107399500</v>
       </c>
-      <c r="C28" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+      <c r="E28" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B29" s="3">
+        <v>45340</v>
+      </c>
+      <c r="C29" t="s">
         <v>32</v>
       </c>
-      <c r="B29">
+      <c r="D29">
         <v>7107399400</v>
       </c>
-      <c r="C29" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
+      <c r="E29" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B30" s="3">
+        <v>28230</v>
+      </c>
+      <c r="C30" t="s">
         <v>33</v>
       </c>
-      <c r="B30">
+      <c r="D30">
         <v>7107399100</v>
       </c>
-      <c r="C30" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+      <c r="E30" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B31" s="3"/>
+      <c r="C31" t="s">
         <v>34</v>
       </c>
-      <c r="B31">
+      <c r="D31">
         <v>7114446</v>
       </c>
-      <c r="C31" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+      <c r="E31" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B32" s="3"/>
+      <c r="C32" t="s">
         <v>35</v>
       </c>
-      <c r="B32">
+      <c r="D32">
         <v>7115297</v>
       </c>
-      <c r="C32" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
+      <c r="E32" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B33" s="3"/>
+      <c r="C33" t="s">
         <v>36</v>
       </c>
-      <c r="B33">
+      <c r="D33">
         <v>7114654</v>
       </c>
-      <c r="C33" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
+      <c r="E33" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B34" s="3"/>
+      <c r="C34" t="s">
         <v>37</v>
       </c>
-      <c r="B34">
+      <c r="D34">
         <v>7115298</v>
       </c>
-      <c r="C34" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
+      <c r="E34" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B35" s="3"/>
+      <c r="C35" t="s">
         <v>38</v>
       </c>
-      <c r="B35">
+      <c r="D35">
         <v>7114697</v>
       </c>
-      <c r="C35" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
+      <c r="E35" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="36" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B36" s="3"/>
+      <c r="C36" t="s">
         <v>39</v>
       </c>
-      <c r="B36">
+      <c r="D36">
         <v>7115089</v>
       </c>
-      <c r="C36" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
+      <c r="E36" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B37" s="3"/>
+      <c r="C37" t="s">
         <v>40</v>
       </c>
-      <c r="B37">
+      <c r="D37">
         <v>7121379</v>
       </c>
-      <c r="C37" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
+      <c r="E37" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="38" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B38" s="3">
+        <v>11379</v>
+      </c>
+      <c r="C38" t="s">
         <v>41</v>
       </c>
-      <c r="B38">
+      <c r="D38">
         <v>7120061100</v>
       </c>
-      <c r="C38" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
+      <c r="E38" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="39" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B39" s="3">
+        <v>28823</v>
+      </c>
+      <c r="C39" t="s">
         <v>42</v>
       </c>
-      <c r="B39">
+      <c r="D39">
         <v>7119999</v>
       </c>
-      <c r="C39" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
+      <c r="E39" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B40" s="3">
+        <v>11379</v>
+      </c>
+      <c r="C40" t="s">
         <v>43</v>
       </c>
-      <c r="B40">
+      <c r="D40">
         <v>7120061100</v>
       </c>
-      <c r="C40" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
+      <c r="E40" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="41" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B41" s="3">
+        <v>35008</v>
+      </c>
+      <c r="C41" t="s">
         <v>44</v>
       </c>
-      <c r="B41">
+      <c r="D41">
         <v>7120060100</v>
       </c>
-      <c r="C41" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>44</v>
-      </c>
-      <c r="B42">
-        <v>7120060100</v>
+      <c r="E41" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B42" s="3">
+        <v>28823</v>
       </c>
       <c r="C42" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
         <v>45</v>
       </c>
-      <c r="B43">
+      <c r="D42">
         <v>7119999</v>
       </c>
+      <c r="E42" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="43" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B43" s="3">
+        <v>7703</v>
+      </c>
       <c r="C43" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
         <v>46</v>
       </c>
-      <c r="B44">
+      <c r="D43">
         <v>7103554106</v>
       </c>
+      <c r="E43" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="44" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B44" s="3">
+        <v>35107</v>
+      </c>
       <c r="C44" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
         <v>47</v>
       </c>
-      <c r="B45">
+      <c r="D44">
         <v>7103555109</v>
       </c>
+      <c r="E44" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="45" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B45" s="3">
+        <v>38594</v>
+      </c>
       <c r="C45" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
         <v>48</v>
       </c>
-      <c r="B46">
+      <c r="D45">
         <v>7103555104</v>
       </c>
-      <c r="C46" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A47" s="1" t="s">
+      <c r="E45" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="46" spans="2:5" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="B46" s="3"/>
+      <c r="C46" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B47">
+      <c r="D46">
         <v>7115248</v>
       </c>
-      <c r="C47" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A48" s="2" t="s">
+      <c r="E46" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="47" spans="2:5" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="B47" s="3">
+        <v>38594</v>
+      </c>
+      <c r="C47" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B48">
+      <c r="D47">
         <v>7103617</v>
       </c>
-      <c r="C48" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A49" s="1" t="s">
+      <c r="E47" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="48" spans="2:5" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="B48" s="3">
+        <v>28802</v>
+      </c>
+      <c r="C48" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B49">
+      <c r="D48">
         <v>7101157</v>
       </c>
-      <c r="C49" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A50" s="1" t="s">
+      <c r="E48" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="B49" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C49" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B50" s="1">
+      <c r="D49" s="1">
         <v>7105917</v>
       </c>
-      <c r="C50" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A51" s="2" t="s">
+      <c r="E49" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="B50" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C50" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="D50" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C51" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A52" s="1" t="s">
+      <c r="E50" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="B51" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C51" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B52">
+      <c r="D51">
         <v>7104999</v>
       </c>
-      <c r="C52" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A53" s="1" t="s">
+      <c r="E51" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="B52" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C52" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B53">
+      <c r="D52">
         <v>7105429</v>
       </c>
-      <c r="C53" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A54" s="1" t="s">
+      <c r="E52" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="B53" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C53" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B54">
+      <c r="D53">
         <v>7105429</v>
       </c>
+      <c r="E53" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B54" s="3" t="s">
+        <v>61</v>
+      </c>
       <c r="C54" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
         <v>58</v>
       </c>
-      <c r="B55">
+      <c r="D54">
         <v>7101205</v>
       </c>
-      <c r="C55" t="s">
+      <c r="E54" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A55" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B55" t="s">
+        <v>69</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D55">
+        <v>7102671500</v>
+      </c>
+      <c r="E55" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B56" t="s">
+        <v>70</v>
+      </c>
+      <c r="D56">
+        <v>7102671100</v>
+      </c>
+      <c r="E56" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A57" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B57" t="s">
+        <v>71</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D57">
+        <v>7102671400</v>
+      </c>
+      <c r="E57" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B58" t="s">
+        <v>72</v>
+      </c>
+      <c r="D58">
+        <v>7102671300</v>
+      </c>
+      <c r="E58" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B59" t="s">
+        <v>73</v>
+      </c>
+      <c r="D59">
+        <v>7102671200</v>
+      </c>
+      <c r="E59" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B60" t="s">
+        <v>74</v>
+      </c>
+      <c r="D60">
+        <v>7102671100</v>
+      </c>
+      <c r="E60" t="s">
         <v>21</v>
       </c>
     </row>

--- a/data/clients.xlsx
+++ b/data/clients.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hoffmann-my.sharepoint.com/personal/lucian_ilade_hoffmann-group_com/Documents/Documentos/Proyectos/pedidos_eb/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="162" documentId="11_F25DC773A252ABDACC10484161DD59B05BDE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5F07651F-3495-4874-B0F5-F79E17AB95BD}"/>
+  <xr:revisionPtr revIDLastSave="170" documentId="11_F25DC773A252ABDACC10484161DD59B05BDE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33B50A94-FCD0-42D0-8D45-468464D0C334}"/>
   <bookViews>
-    <workbookView xWindow="-135" yWindow="-135" windowWidth="29070" windowHeight="17550" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="81">
   <si>
     <t>Patentes Talgo, S.L.U. Centro: 86 TALLERES MTO. ALTA VELOCIDAD Antonio Cabezón s/n 28034 Madrid-Madrid España</t>
   </si>
@@ -295,6 +295,15 @@
   </si>
   <si>
     <t>PT501486429</t>
+  </si>
+  <si>
+    <t>PT980671566</t>
+  </si>
+  <si>
+    <t>7005-797</t>
+  </si>
+  <si>
+    <t>Mecachrome Aeronautica Unipessoal Lda Parque Ind.de Aeronautica Lote B 7005-797 EVORA-SETUBAL PORTUGAL</t>
   </si>
 </sst>
 </file>
@@ -350,7 +359,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -359,6 +368,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -643,10 +655,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F60"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="112.5546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="46.5546875" customWidth="1"/>
@@ -1469,6 +1481,23 @@
         <v>21</v>
       </c>
     </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>78</v>
+      </c>
+      <c r="B61" t="s">
+        <v>79</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="D61">
+        <v>7110865</v>
+      </c>
+      <c r="E61" t="s">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/data/clients.xlsx
+++ b/data/clients.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hoffmann-my.sharepoint.com/personal/lucian_ilade_hoffmann-group_com/Documents/Documentos/Proyectos/pedidos_eb/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="170" documentId="11_F25DC773A252ABDACC10484161DD59B05BDE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33B50A94-FCD0-42D0-8D45-468464D0C334}"/>
+  <xr:revisionPtr revIDLastSave="172" documentId="11_F25DC773A252ABDACC10484161DD59B05BDE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3B0F1D6-7E3A-4AD4-B6B2-D5248107293D}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -297,13 +297,13 @@
     <t>PT501486429</t>
   </si>
   <si>
-    <t>PT980671566</t>
-  </si>
-  <si>
     <t>7005-797</t>
   </si>
   <si>
     <t>Mecachrome Aeronautica Unipessoal Lda Parque Ind.de Aeronautica Lote B 7005-797 EVORA-SETUBAL PORTUGAL</t>
+  </si>
+  <si>
+    <t>PT513009264</t>
   </si>
 </sst>
 </file>
@@ -1482,14 +1482,14 @@
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
+      <c r="A61" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B61" t="s">
         <v>78</v>
       </c>
-      <c r="B61" t="s">
+      <c r="C61" s="6" t="s">
         <v>79</v>
-      </c>
-      <c r="C61" s="6" t="s">
-        <v>80</v>
       </c>
       <c r="D61">
         <v>7110865</v>

--- a/data/clients.xlsx
+++ b/data/clients.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hoffmann-my.sharepoint.com/personal/lucian_ilade_hoffmann-group_com/Documents/Documentos/Proyectos/pedidos_eb/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="172" documentId="11_F25DC773A252ABDACC10484161DD59B05BDE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3B0F1D6-7E3A-4AD4-B6B2-D5248107293D}"/>
+  <xr:revisionPtr revIDLastSave="179" documentId="11_F25DC773A252ABDACC10484161DD59B05BDE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{250C6DBC-1107-45DA-8A2E-78EB1D1E98C2}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="39735" yWindow="3750" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="84">
   <si>
     <t>Patentes Talgo, S.L.U. Centro: 86 TALLERES MTO. ALTA VELOCIDAD Antonio Cabezón s/n 28034 Madrid-Madrid España</t>
   </si>
@@ -304,6 +304,20 @@
   </si>
   <si>
     <t>PT513009264</t>
+  </si>
+  <si>
+    <t>PT502322004</t>
+  </si>
+  <si>
+    <t>4760-810</t>
+  </si>
+  <si>
+    <t>Continental Mabor
+Industria de Pneus, S.A.
+Rua de Montoito
+(Coord.: 41.357190, -8.542773)
+4760-810 Lousado - VNF
+PORTUGAL</t>
   </si>
 </sst>
 </file>
@@ -655,7 +669,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -1498,6 +1512,23 @@
         <v>21</v>
       </c>
     </row>
+    <row r="62" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>81</v>
+      </c>
+      <c r="B62" t="s">
+        <v>82</v>
+      </c>
+      <c r="C62" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="D62">
+        <v>7102278</v>
+      </c>
+      <c r="E62" t="s">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
